--- a/Lab3/Testcase_Lab3_673380290-9.xlsx
+++ b/Lab3/Testcase_Lab3_673380290-9.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="87">
   <si>
     <t>Use case ID/ Req. ID</t>
   </si>
@@ -187,14 +187,15 @@
     <t>เมธอด return ผลลัพธ์เป็น VRIWZDUH</t>
   </si>
   <si>
-    <t>ขัดแย้งกับ requirement ที่เนื่องจาก lowercase 
-ที่ออกมาจะต้องเป็น a-z ในขณะที่ requirement 
-ต้องการให้ออกมาเป็น uppercase ทั้งหมด 
-และการ shift จะต้องเลือกจำนวน key ที่ต้องการได้เสมอ
-และเคสที่ได้ทดสอบ จำนวนคีย์ใน expected result ยังไม่ถูกต้อง</t>
+    <t>เคสที่ได้ทดสอบ จำนวนคีย์ใน expected result = 7 ซึ่งยังไม่ถูกต้อง
+และการก่อนเข้ารหัสจะแปลงเป็น Uppercase ก่อนเสมอจึงไม่สามารถแยกแยะ
+พิมพ์ใหญ่เล็กได้</t>
   </si>
   <si>
     <t>2. message เป็นตัวอักษร a-z จะให้ผลลัพธ์เป็น a-z</t>
+  </si>
+  <si>
+    <t>เมธอด return ผลลัพธ์เป็น "zvmadhyl"</t>
   </si>
   <si>
     <t>2. key = 3</t>
@@ -266,16 +267,13 @@
     <t>software</t>
   </si>
   <si>
-    <t>เมธอด return ผลลัพธ์เป็น "zvmadhyl"</t>
-  </si>
-  <si>
     <t>TC03</t>
   </si>
   <si>
     <t>Hello KKU61</t>
   </si>
   <si>
-    <t>เมธอด return ผลลัพธ์เป็น "MJQQT PPZ61"</t>
+    <t>เมธอด return ผลลัพธ์เป็น "KHOOR NNX61"</t>
   </si>
   <si>
     <t>TC04</t>
@@ -474,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -562,7 +560,7 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -571,6 +569,9 @@
     <xf borderId="5" fillId="5" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -30141,22 +30142,24 @@
       <c r="D10" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="36"/>
+      <c r="E10" s="38" t="s">
+        <v>57</v>
+      </c>
       <c r="F10" s="36"/>
       <c r="G10" s="36"/>
       <c r="H10" s="36"/>
     </row>
     <row r="11">
-      <c r="A11" s="38"/>
-      <c r="B11" s="38"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="39"/>
       <c r="C11" s="37"/>
       <c r="D11" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
     </row>
     <row r="12">
       <c r="A12" s="37"/>
@@ -30219,22 +30222,22 @@
       <c r="H17" s="37"/>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="s">
-        <v>58</v>
+      <c r="A18" s="40" t="s">
+        <v>59</v>
       </c>
-      <c r="B18" s="40" t="s">
-        <v>59</v>
+      <c r="B18" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="12"/>
     </row>
     <row r="19">
-      <c r="A19" s="41"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -31217,11 +31220,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="13">
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="B18:E18"/>
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="G9:G11"/>
     <mergeCell ref="H9:H11"/>
@@ -31232,6 +31233,7 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A7:E7"/>
+    <mergeCell ref="B18:E18"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -31286,8 +31288,8 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="42" t="s">
-        <v>60</v>
+      <c r="A2" s="43" t="s">
+        <v>61</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -31295,25 +31297,25 @@
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
       <c r="G2" s="12"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
     </row>
     <row r="3" ht="24.0" customHeight="1">
       <c r="A3" s="1"/>
@@ -31344,16 +31346,16 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" ht="24.0" customHeight="1">
-      <c r="A4" s="44" t="s">
-        <v>61</v>
+      <c r="A4" s="45" t="s">
+        <v>62</v>
       </c>
-      <c r="B4" s="45" t="s">
-        <v>62</v>
+      <c r="B4" s="46" t="s">
+        <v>63</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="44" t="s">
-        <v>63</v>
+      <c r="E4" s="45" t="s">
+        <v>64</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>28</v>
@@ -31380,19 +31382,19 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" ht="24.0" customHeight="1">
-      <c r="A5" s="44" t="s">
-        <v>64</v>
+      <c r="A5" s="45" t="s">
+        <v>65</v>
       </c>
-      <c r="B5" s="45" t="s">
-        <v>65</v>
+      <c r="B5" s="46" t="s">
+        <v>66</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
-      <c r="E5" s="44" t="s">
-        <v>66</v>
+      <c r="E5" s="45" t="s">
+        <v>67</v>
       </c>
-      <c r="F5" s="46" t="s">
-        <v>67</v>
+      <c r="F5" s="47" t="s">
+        <v>68</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="1"/>
@@ -31416,10 +31418,10 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" ht="24.0" customHeight="1">
-      <c r="A6" s="47" t="s">
-        <v>68</v>
+      <c r="A6" s="48" t="s">
+        <v>69</v>
       </c>
-      <c r="B6" s="48"/>
+      <c r="B6" s="49"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -31474,86 +31476,86 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" ht="24.0" customHeight="1">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="49" t="s">
-        <v>69</v>
+      <c r="B8" s="50" t="s">
+        <v>70</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="51" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="12"/>
-      <c r="E8" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="49" t="s">
+      <c r="E8" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="F8" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="51"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-    </row>
-    <row r="9" ht="24.0" customHeight="1">
-      <c r="A9" s="38"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="52" t="s">
+      <c r="G8" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="52"/>
+      <c r="Q8" s="52"/>
+      <c r="R8" s="52"/>
+      <c r="S8" s="52"/>
+      <c r="T8" s="52"/>
+      <c r="U8" s="52"/>
+      <c r="V8" s="52"/>
+      <c r="W8" s="52"/>
+      <c r="X8" s="52"/>
+      <c r="Y8" s="52"/>
+      <c r="Z8" s="52"/>
+    </row>
+    <row r="9" ht="24.0" customHeight="1">
+      <c r="A9" s="39"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
+      <c r="D9" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
+      <c r="P9" s="52"/>
+      <c r="Q9" s="52"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="52"/>
+      <c r="T9" s="52"/>
+      <c r="U9" s="52"/>
+      <c r="V9" s="52"/>
+      <c r="W9" s="52"/>
+      <c r="X9" s="52"/>
+      <c r="Y9" s="52"/>
+      <c r="Z9" s="52"/>
     </row>
     <row r="10" ht="24.0" customHeight="1">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="55" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D10" s="9">
         <v>3.0</v>
@@ -31561,8 +31563,8 @@
       <c r="E10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="55" t="s">
-        <v>77</v>
+      <c r="F10" s="56" t="s">
+        <v>78</v>
       </c>
       <c r="G10" s="14"/>
       <c r="H10" s="1"/>
@@ -31588,19 +31590,19 @@
     <row r="11" ht="24.0" customHeight="1">
       <c r="A11" s="36"/>
       <c r="B11" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" s="9">
         <v>3.0</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
-      <c r="F11" s="55" t="s">
-        <v>77</v>
+      <c r="F11" s="56" t="s">
+        <v>78</v>
       </c>
       <c r="G11" s="14"/>
       <c r="H11" s="1"/>
@@ -31628,19 +31630,19 @@
       <c r="B12" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="55">
-        <v>5.0</v>
+      <c r="D12" s="56">
+        <v>3.0</v>
       </c>
-      <c r="E12" s="55" t="s">
+      <c r="E12" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="F12" s="55" t="s">
+      <c r="F12" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="56"/>
+      <c r="G12" s="57"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -31662,23 +31664,23 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" ht="24.0" customHeight="1">
-      <c r="A13" s="38"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="56">
         <v>3.0</v>
       </c>
-      <c r="E13" s="55" t="s">
+      <c r="E13" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="55" t="s">
+      <c r="F13" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="G13" s="56"/>
+      <c r="G13" s="57"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>

--- a/Lab3/Testcase_Lab3_673380290-9.xlsx
+++ b/Lab3/Testcase_Lab3_673380290-9.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="96">
   <si>
     <t>Use case ID/ Req. ID</t>
   </si>
@@ -94,6 +94,27 @@
   </si>
   <si>
     <t>Defect Details</t>
+  </si>
+  <si>
+    <t>RM01</t>
+  </si>
+  <si>
+    <t>คีย์ไม่ตรง</t>
+  </si>
+  <si>
+    <t>วัชรพล</t>
+  </si>
+  <si>
+    <t>คีย์ที่ผลลัพธ์ที่คาดหวังต้องเป็น 7 ถึงจะได้ตามคาดจริงออกมาเป็น fail ในซีนนี้</t>
+  </si>
+  <si>
+    <t>DF02</t>
+  </si>
+  <si>
+    <t>ไม่รองรับ lowercase</t>
+  </si>
+  <si>
+    <t>ไม่สามารถ output เป็น lowercase ได้ตามที่คาดหวัง</t>
   </si>
   <si>
     <t>Test Scenario ID:</t>
@@ -187,15 +208,16 @@
     <t>เมธอด return ผลลัพธ์เป็น VRIWZDUH</t>
   </si>
   <si>
-    <t>เคสที่ได้ทดสอบ จำนวนคีย์ใน expected result = 7 ซึ่งยังไม่ถูกต้อง
-และการก่อนเข้ารหัสจะแปลงเป็น Uppercase ก่อนเสมอจึงไม่สามารถแยกแยะ
-พิมพ์ใหญ่เล็กได้</t>
-  </si>
-  <si>
     <t>2. message เป็นตัวอักษร a-z จะให้ผลลัพธ์เป็น a-z</t>
   </si>
   <si>
     <t>เมธอด return ผลลัพธ์เป็น "zvmadhyl"</t>
+  </si>
+  <si>
+    <t>เมธอด return ผลลัพธ์เป็น invalid</t>
+  </si>
+  <si>
+    <t>DF01</t>
   </si>
   <si>
     <t>2. key = 3</t>
@@ -258,7 +280,7 @@
     <t>SOFTWARE</t>
   </si>
   <si>
-    <t>เมธอด return มาเป็น VRIWZDUH</t>
+    <t>เมธอด return มาเป็น "VRIWZDUH"</t>
   </si>
   <si>
     <t>TC02</t>
@@ -267,22 +289,25 @@
     <t>software</t>
   </si>
   <si>
+    <t>เมธอด return มาเป็น "invalid"</t>
+  </si>
+  <si>
     <t>TC03</t>
   </si>
   <si>
-    <t>Hello KKU61</t>
+    <t>KKU</t>
   </si>
   <si>
-    <t>เมธอด return ผลลัพธ์เป็น "KHOOR NNX61"</t>
+    <t>เมธอด return ผลลัพธ์เป็น "PPZ"</t>
   </si>
   <si>
     <t>TC04</t>
   </si>
   <si>
-    <t>XyZ+-*/</t>
+    <t>เมธอดควร return ผลลัพธ์เป็น "invalid"</t>
   </si>
   <si>
-    <t>เมธอด return ผลลัพธ์เป็น "ABC+-*/"</t>
+    <t>เมธอด return ผลลัพธ์เป็น "invalid"</t>
   </si>
 </sst>
 </file>
@@ -342,7 +367,7 @@
       <name val="TH Sarabun PSK"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,18 +388,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFFFC000"/>
       </patternFill>
@@ -383,6 +396,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFBE4D5"/>
         <bgColor rgb="FFFBE4D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,12 +523,13 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="5" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -519,7 +539,7 @@
       <alignment horizontal="left" readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -539,7 +559,7 @@
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -558,17 +578,20 @@
       <alignment vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="top"/>
     </xf>
@@ -615,10 +638,8 @@
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1089,9 +1110,15 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="12"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="14"/>
+      <c r="D8" s="13">
+        <v>4.0</v>
+      </c>
+      <c r="E8" s="13">
+        <v>2.0</v>
+      </c>
+      <c r="F8" s="13">
+        <v>2.0</v>
+      </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="8" t="s">
@@ -28928,67 +28955,89 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17">
+      <c r="A3" s="16">
         <v>1.0</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="B3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="18">
+        <v>46211.0</v>
+      </c>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="17" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
+      <c r="A4" s="17">
+        <v>2.0</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="18">
+        <v>46211.0</v>
+      </c>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -29997,86 +30046,86 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="s">
-        <v>25</v>
+      <c r="A1" s="19" t="s">
+        <v>32</v>
       </c>
-      <c r="B1" s="21" t="s">
-        <v>26</v>
+      <c r="B1" s="20" t="s">
+        <v>33</v>
       </c>
-      <c r="C1" s="20" t="s">
-        <v>27</v>
+      <c r="C1" s="19" t="s">
+        <v>34</v>
       </c>
-      <c r="D1" s="22" t="s">
-        <v>28</v>
+      <c r="D1" s="21" t="s">
+        <v>35</v>
       </c>
       <c r="E1" s="12"/>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="s">
-        <v>29</v>
+      <c r="A2" s="19" t="s">
+        <v>36</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>30</v>
+      <c r="C2" s="19" t="s">
+        <v>37</v>
       </c>
-      <c r="D2" s="22" t="s">
-        <v>31</v>
+      <c r="D2" s="21" t="s">
+        <v>38</v>
       </c>
       <c r="E2" s="12"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="s">
-        <v>32</v>
+      <c r="A3" s="19" t="s">
+        <v>39</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="20" t="s">
-        <v>33</v>
+      <c r="B3" s="20"/>
+      <c r="C3" s="19" t="s">
+        <v>40</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>31</v>
+      <c r="D3" s="21" t="s">
+        <v>38</v>
       </c>
       <c r="E3" s="12"/>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="s">
-        <v>34</v>
+      <c r="A4" s="19" t="s">
+        <v>41</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>35</v>
+      <c r="B4" s="22" t="s">
+        <v>42</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>36</v>
+      <c r="C4" s="23" t="s">
+        <v>43</v>
       </c>
-      <c r="D4" s="25"/>
+      <c r="D4" s="24"/>
       <c r="E4" s="12"/>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="s">
-        <v>37</v>
+      <c r="A5" s="19" t="s">
+        <v>44</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>38</v>
+      <c r="B5" s="21" t="s">
+        <v>45</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="12"/>
     </row>
     <row r="6" ht="124.5" customHeight="1">
-      <c r="A6" s="24" t="s">
-        <v>39</v>
+      <c r="A6" s="23" t="s">
+        <v>46</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>40</v>
+      <c r="B6" s="21" t="s">
+        <v>47</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="12"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="s">
-        <v>41</v>
+      <c r="A7" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -30084,149 +30133,153 @@
       <c r="E7" s="12"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="s">
-        <v>42</v>
+      <c r="A8" s="26" t="s">
+        <v>49</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>43</v>
+      <c r="B8" s="26" t="s">
+        <v>50</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>44</v>
+      <c r="C8" s="26" t="s">
+        <v>51</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" ht="132.0" customHeight="1">
+      <c r="A9" s="28">
+        <v>1.0</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="34"/>
+      <c r="H9" s="33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" ht="88.5" customHeight="1">
-      <c r="A9" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>56</v>
+      <c r="D10" s="37" t="s">
+        <v>62</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
+      <c r="F10" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="34"/>
+      <c r="H10" s="33" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="39"/>
       <c r="B11" s="39"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37" t="s">
-        <v>58</v>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36" t="s">
+        <v>66</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
+      <c r="A12" s="36"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
     </row>
     <row r="13">
-      <c r="A13" s="37"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
+      <c r="A13" s="36"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
     </row>
     <row r="14">
-      <c r="A14" s="37"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
+      <c r="A14" s="36"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
     </row>
     <row r="15">
-      <c r="A15" s="37"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
+      <c r="A15" s="36"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
     </row>
     <row r="16">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
+      <c r="A16" s="36"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
     </row>
     <row r="17">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
     </row>
     <row r="18">
       <c r="A18" s="40" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -31220,12 +31273,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="10">
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="H9:H11"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
@@ -31289,7 +31339,7 @@
     </row>
     <row r="2" ht="24.0" customHeight="1">
       <c r="A2" s="43" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -31347,18 +31397,18 @@
     </row>
     <row r="4" ht="24.0" customHeight="1">
       <c r="A4" s="45" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="45" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
-      <c r="F4" s="22" t="s">
-        <v>28</v>
+      <c r="F4" s="21" t="s">
+        <v>35</v>
       </c>
       <c r="G4" s="12"/>
       <c r="H4" s="1"/>
@@ -31383,18 +31433,18 @@
     </row>
     <row r="5" ht="24.0" customHeight="1">
       <c r="A5" s="45" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="45" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F5" s="47" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="1"/>
@@ -31419,7 +31469,7 @@
     </row>
     <row r="6" ht="24.0" customHeight="1">
       <c r="A6" s="48" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B6" s="49"/>
       <c r="C6" s="11"/>
@@ -31480,20 +31530,20 @@
         <v>1</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="50" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="52"/>
@@ -31519,10 +31569,10 @@
       <c r="A9" s="39"/>
       <c r="B9" s="39"/>
       <c r="C9" s="53" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
@@ -31552,21 +31602,21 @@
         <v>10</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D10" s="9">
         <v>3.0</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
-      <c r="F10" s="56" t="s">
-        <v>78</v>
+      <c r="F10" s="13" t="s">
+        <v>86</v>
       </c>
-      <c r="G10" s="14"/>
+      <c r="G10" s="56"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -31588,23 +31638,23 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" ht="24.0" customHeight="1">
-      <c r="A11" s="36"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D11" s="9">
         <v>3.0</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
-      <c r="F11" s="56" t="s">
-        <v>78</v>
+      <c r="F11" s="13" t="s">
+        <v>89</v>
       </c>
-      <c r="G11" s="14"/>
+      <c r="G11" s="56"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -31626,21 +31676,21 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" ht="24.0" customHeight="1">
-      <c r="A12" s="36"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="9" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
-      <c r="C12" s="56" t="s">
-        <v>82</v>
+      <c r="C12" s="13" t="s">
+        <v>91</v>
       </c>
-      <c r="D12" s="56">
-        <v>3.0</v>
+      <c r="D12" s="13">
+        <v>5.0</v>
       </c>
-      <c r="E12" s="56" t="s">
-        <v>83</v>
+      <c r="E12" s="13" t="s">
+        <v>92</v>
       </c>
-      <c r="F12" s="56" t="s">
-        <v>83</v>
+      <c r="F12" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="G12" s="57"/>
       <c r="H12" s="1"/>
@@ -31666,19 +31716,19 @@
     <row r="13" ht="24.0" customHeight="1">
       <c r="A13" s="39"/>
       <c r="B13" s="9" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
-      <c r="C13" s="56" t="s">
-        <v>85</v>
+      <c r="C13" s="13">
+        <v>1234.0</v>
       </c>
-      <c r="D13" s="56">
+      <c r="D13" s="13">
         <v>3.0</v>
       </c>
-      <c r="E13" s="56" t="s">
-        <v>86</v>
+      <c r="E13" s="13" t="s">
+        <v>94</v>
       </c>
-      <c r="F13" s="56" t="s">
-        <v>86</v>
+      <c r="F13" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="G13" s="57"/>
       <c r="H13" s="1"/>
